--- a/upload/KOMPARASI KOMPONEN KPI CP TEGALBOTO v2.xlsx
+++ b/upload/KOMPARASI KOMPONEN KPI CP TEGALBOTO v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/652a339dafd796b4/Desktop/KPI TEGALBOTO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{245CA8CC-C876-254E-B55B-66F8F8D6C1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{617DFA54-CBAB-44A0-AECE-FCF4636139DD}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{245CA8CC-C876-254E-B55B-66F8F8D6C1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D041207-8E38-46AF-9DAD-C31E395B8F4C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{03C51708-DF73-47C6-914D-74E8D146F623}"/>
   </bookViews>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -185,9 +183,6 @@
     <t>1,530,15%</t>
   </si>
   <si>
-    <t>CP TEGALBOTO</t>
-  </si>
-  <si>
     <t>UPC BASUKI RAHMAT</t>
   </si>
   <si>
@@ -201,6 +196,9 @@
   </si>
   <si>
     <t>BRI UNIT SUMBERJATI</t>
+  </si>
+  <si>
+    <t>UPC TEGALBOTO</t>
   </si>
 </sst>
 </file>
@@ -891,6 +889,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1193,7 +1195,7 @@
   <cols>
     <col min="1" max="1" width="24.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -1203,7 +1205,7 @@
   <sheetData>
     <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1909,7 +1911,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="19"/>
@@ -2615,7 +2617,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -3321,7 +3323,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
@@ -4027,7 +4029,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
@@ -4732,7 +4734,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B147" s="19"/>
       <c r="C147" s="19"/>
